--- a/Năng suất lao động phân theo địa phương. Đơn vị tính Triệu đồng_người.xlsx
+++ b/Năng suất lao động phân theo địa phương. Đơn vị tính Triệu đồng_người.xlsx
@@ -16,7 +16,7 @@
     <t>Sơ bộ 2021</t>
   </si>
   <si>
-    <t>Ước tính 2022</t>
+    <t>Sơ bộ 2022</t>
   </si>
   <si>
     <t>CẢ NƯỚC</t>
